--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P1376_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P1376_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.6332519022093325</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6769290861434174</v>
+        <v>0.821721103397907</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.6332519022093325</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6769290861434173</v>
+        <v>0.821721103397907</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5403673882005813</v>
+        <v>0.3686136478428049</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7188791760896567</v>
+        <v>0.7315594959885379</v>
       </c>
       <c r="G2" t="n">
-        <v>0.998915148061319</v>
+        <v>0.9993095835505734</v>
       </c>
       <c r="H2" t="n">
-        <v>0.999417524526577</v>
+        <v>0.9997232907628104</v>
       </c>
       <c r="I2" t="n">
-        <v>0.697008547008547</v>
+        <v>0.7658119658119659</v>
       </c>
     </row>
   </sheetData>
